--- a/vix_pkg/data/all_etfs_oos_predictions.xlsx
+++ b/vix_pkg/data/all_etfs_oos_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I503"/>
+  <dimension ref="A1:I522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15032,6 +15032,557 @@
         <v>586.08</v>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" s="1" t="n">
+        <v>502</v>
+      </c>
+      <c r="B504" s="2" t="n">
+        <v>45659</v>
+      </c>
+      <c r="C504" t="n">
+        <v>-0.02312702371253038</v>
+      </c>
+      <c r="D504" t="n">
+        <v>0.06185888041465494</v>
+      </c>
+      <c r="E504" t="n">
+        <v>0.03229151995009766</v>
+      </c>
+      <c r="F504" t="n">
+        <v>-0.09039843478720144</v>
+      </c>
+      <c r="G504" t="n">
+        <v>0.01031998289472464</v>
+      </c>
+      <c r="H504" t="n">
+        <v>-0.01877010144687383</v>
+      </c>
+      <c r="I504" t="n">
+        <v>584.64</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="n">
+        <v>503</v>
+      </c>
+      <c r="B505" s="2" t="n">
+        <v>45660</v>
+      </c>
+      <c r="C505" t="n">
+        <v>0.04996116822489845</v>
+      </c>
+      <c r="D505" t="n">
+        <v>-0.02038320361484391</v>
+      </c>
+      <c r="E505" t="n">
+        <v>-0.08837166445659746</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0.03053285645736102</v>
+      </c>
+      <c r="G505" t="n">
+        <v>-0.01725966255163794</v>
+      </c>
+      <c r="H505" t="n">
+        <v>0.00840065361114151</v>
+      </c>
+      <c r="I505" t="n">
+        <v>591.95</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="n">
+        <v>504</v>
+      </c>
+      <c r="B506" s="2" t="n">
+        <v>45663</v>
+      </c>
+      <c r="C506" t="n">
+        <v>0.01182548098719034</v>
+      </c>
+      <c r="D506" t="n">
+        <v>-0.05328714817286151</v>
+      </c>
+      <c r="E506" t="n">
+        <v>-0.004092073378985981</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0.07781049963568486</v>
+      </c>
+      <c r="G506" t="n">
+        <v>-0.01261399708626292</v>
+      </c>
+      <c r="H506" t="n">
+        <v>0.01664235726567136</v>
+      </c>
+      <c r="I506" t="n">
+        <v>595.36</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="n">
+        <v>505</v>
+      </c>
+      <c r="B507" s="2" t="n">
+        <v>45664</v>
+      </c>
+      <c r="C507" t="n">
+        <v>-0.06380567447765113</v>
+      </c>
+      <c r="D507" t="n">
+        <v>0.01846725238040957</v>
+      </c>
+      <c r="E507" t="n">
+        <v>0.08495901923122308</v>
+      </c>
+      <c r="F507" t="n">
+        <v>-0.0270561076067075</v>
+      </c>
+      <c r="G507" t="n">
+        <v>0.03055790386839078</v>
+      </c>
+      <c r="H507" t="n">
+        <v>-0.005777388909299696</v>
+      </c>
+      <c r="I507" t="n">
+        <v>588.63</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="n">
+        <v>506</v>
+      </c>
+      <c r="B508" s="2" t="n">
+        <v>45665</v>
+      </c>
+      <c r="C508" t="n">
+        <v>0.005240933847268937</v>
+      </c>
+      <c r="D508" t="n">
+        <v>-0.06796931570195755</v>
+      </c>
+      <c r="E508" t="n">
+        <v>-0.009936163232387664</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0.1005658167481281</v>
+      </c>
+      <c r="G508" t="n">
+        <v>0.003414150861632531</v>
+      </c>
+      <c r="H508" t="n">
+        <v>0.02874366535262519</v>
+      </c>
+      <c r="I508" t="n">
+        <v>589.49</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="n">
+        <v>507</v>
+      </c>
+      <c r="B509" s="2" t="n">
+        <v>45667</v>
+      </c>
+      <c r="C509" t="n">
+        <v>-0.06735715952675636</v>
+      </c>
+      <c r="D509" t="n">
+        <v>0.03820400854948413</v>
+      </c>
+      <c r="E509" t="n">
+        <v>0.09388261167621963</v>
+      </c>
+      <c r="F509" t="n">
+        <v>-0.05609158926532075</v>
+      </c>
+      <c r="G509" t="n">
+        <v>0.03483269162757669</v>
+      </c>
+      <c r="H509" t="n">
+        <v>-0.01384709329173031</v>
+      </c>
+      <c r="I509" t="n">
+        <v>580.49</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="n">
+        <v>508</v>
+      </c>
+      <c r="B510" s="2" t="n">
+        <v>45670</v>
+      </c>
+      <c r="C510" t="n">
+        <v>0.02127739844728488</v>
+      </c>
+      <c r="D510" t="n">
+        <v>0.01580089369010413</v>
+      </c>
+      <c r="E510" t="n">
+        <v>-0.02809672549386336</v>
+      </c>
+      <c r="F510" t="n">
+        <v>-0.02324316318003137</v>
+      </c>
+      <c r="G510" t="n">
+        <v>0.001973080994994142</v>
+      </c>
+      <c r="H510" t="n">
+        <v>-0.00568809706589038</v>
+      </c>
+      <c r="I510" t="n">
+        <v>581.39</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="n">
+        <v>509</v>
+      </c>
+      <c r="B511" s="2" t="n">
+        <v>45671</v>
+      </c>
+      <c r="C511" t="n">
+        <v>0.0167018338220834</v>
+      </c>
+      <c r="D511" t="n">
+        <v>0.1056747445702286</v>
+      </c>
+      <c r="E511" t="n">
+        <v>-0.02982597374990521</v>
+      </c>
+      <c r="F511" t="n">
+        <v>-0.1551956222838119</v>
+      </c>
+      <c r="G511" t="n">
+        <v>-0.01656215370900685</v>
+      </c>
+      <c r="H511" t="n">
+        <v>-0.0355369264487851</v>
+      </c>
+      <c r="I511" t="n">
+        <v>582.1900000000001</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="n">
+        <v>510</v>
+      </c>
+      <c r="B512" s="2" t="n">
+        <v>45672</v>
+      </c>
+      <c r="C512" t="n">
+        <v>0.07765096464161254</v>
+      </c>
+      <c r="D512" t="n">
+        <v>-0.0144471507821117</v>
+      </c>
+      <c r="E512" t="n">
+        <v>-0.1296072390912558</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0.02110770301575631</v>
+      </c>
+      <c r="G512" t="n">
+        <v>-0.02571184327604979</v>
+      </c>
+      <c r="H512" t="n">
+        <v>0.00425423692302655</v>
+      </c>
+      <c r="I512" t="n">
+        <v>592.78</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="n">
+        <v>511</v>
+      </c>
+      <c r="B513" s="2" t="n">
+        <v>45673</v>
+      </c>
+      <c r="C513" t="n">
+        <v>-0.001533777741032535</v>
+      </c>
+      <c r="D513" t="n">
+        <v>-0.009434105118647448</v>
+      </c>
+      <c r="E513" t="n">
+        <v>-0.004186292097161907</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0.01382658224079888</v>
+      </c>
+      <c r="G513" t="n">
+        <v>-0.01241397357068002</v>
+      </c>
+      <c r="H513" t="n">
+        <v>0.001393236629970981</v>
+      </c>
+      <c r="I513" t="n">
+        <v>591.64</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="n">
+        <v>512</v>
+      </c>
+      <c r="B514" s="2" t="n">
+        <v>45674</v>
+      </c>
+      <c r="C514" t="n">
+        <v>-0.006158597226382568</v>
+      </c>
+      <c r="D514" t="n">
+        <v>0.06437730224878958</v>
+      </c>
+      <c r="E514" t="n">
+        <v>0.01250666517397105</v>
+      </c>
+      <c r="F514" t="n">
+        <v>-0.09440707616770511</v>
+      </c>
+      <c r="G514" t="n">
+        <v>0.005536341114339888</v>
+      </c>
+      <c r="H514" t="n">
+        <v>-0.02277664105621653</v>
+      </c>
+      <c r="I514" t="n">
+        <v>597.58</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="n">
+        <v>513</v>
+      </c>
+      <c r="B515" s="2" t="n">
+        <v>45678</v>
+      </c>
+      <c r="C515" t="n">
+        <v>0.04233439549678228</v>
+      </c>
+      <c r="D515" t="n">
+        <v>-0.03344574676817898</v>
+      </c>
+      <c r="E515" t="n">
+        <v>-0.06195252909012993</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0.04963348217092697</v>
+      </c>
+      <c r="G515" t="n">
+        <v>-0.009708771747856568</v>
+      </c>
+      <c r="H515" t="n">
+        <v>0.01375757455660286</v>
+      </c>
+      <c r="I515" t="n">
+        <v>603.05</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="n">
+        <v>514</v>
+      </c>
+      <c r="B516" s="2" t="n">
+        <v>45679</v>
+      </c>
+      <c r="C516" t="n">
+        <v>-0.01341304044662738</v>
+      </c>
+      <c r="D516" t="n">
+        <v>0.02168588372095499</v>
+      </c>
+      <c r="E516" t="n">
+        <v>0.02018071424205007</v>
+      </c>
+      <c r="F516" t="n">
+        <v>-0.03204575048743716</v>
+      </c>
+      <c r="G516" t="n">
+        <v>0.003478211302114949</v>
+      </c>
+      <c r="H516" t="n">
+        <v>-0.01028966806183827</v>
+      </c>
+      <c r="I516" t="n">
+        <v>606.4400000000001</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="n">
+        <v>515</v>
+      </c>
+      <c r="B517" s="2" t="n">
+        <v>45680</v>
+      </c>
+      <c r="C517" t="n">
+        <v>0.01378307666435959</v>
+      </c>
+      <c r="D517" t="n">
+        <v>0.007017743473421666</v>
+      </c>
+      <c r="E517" t="n">
+        <v>-0.02681417863656818</v>
+      </c>
+      <c r="F517" t="n">
+        <v>-0.01013357453331273</v>
+      </c>
+      <c r="G517" t="n">
+        <v>-0.007668190818712144</v>
+      </c>
+      <c r="H517" t="n">
+        <v>-0.0002829998270796903</v>
+      </c>
+      <c r="I517" t="n">
+        <v>609.75</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="n">
+        <v>516</v>
+      </c>
+      <c r="B518" s="2" t="n">
+        <v>45681</v>
+      </c>
+      <c r="C518" t="n">
+        <v>0.002217276038186102</v>
+      </c>
+      <c r="D518" t="n">
+        <v>-0.06877155983010505</v>
+      </c>
+      <c r="E518" t="n">
+        <v>-0.01171567038152712</v>
+      </c>
+      <c r="F518" t="n">
+        <v>0.09997761057605145</v>
+      </c>
+      <c r="G518" t="n">
+        <v>0.0006995613316745972</v>
+      </c>
+      <c r="H518" t="n">
+        <v>0.02060142609563434</v>
+      </c>
+      <c r="I518" t="n">
+        <v>607.97</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="n">
+        <v>517</v>
+      </c>
+      <c r="B519" s="2" t="n">
+        <v>45684</v>
+      </c>
+      <c r="C519" t="n">
+        <v>-0.05852737494056245</v>
+      </c>
+      <c r="D519" t="n">
+        <v>0.02131425219586868</v>
+      </c>
+      <c r="E519" t="n">
+        <v>0.1008046697975389</v>
+      </c>
+      <c r="F519" t="n">
+        <v>-0.03111229343700072</v>
+      </c>
+      <c r="G519" t="n">
+        <v>0.02076200423839051</v>
+      </c>
+      <c r="H519" t="n">
+        <v>-0.005038104885518722</v>
+      </c>
+      <c r="I519" t="n">
+        <v>599.37</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="n">
+        <v>518</v>
+      </c>
+      <c r="B520" s="2" t="n">
+        <v>45685</v>
+      </c>
+      <c r="C520" t="n">
+        <v>0.02053144734400153</v>
+      </c>
+      <c r="D520" t="n">
+        <v>0.009974767119057787</v>
+      </c>
+      <c r="E520" t="n">
+        <v>-0.05742697126361132</v>
+      </c>
+      <c r="F520" t="n">
+        <v>-0.01451521504342848</v>
+      </c>
+      <c r="G520" t="n">
+        <v>-0.02076200423839051</v>
+      </c>
+      <c r="H520" t="n">
+        <v>-0.003999726942341734</v>
+      </c>
+      <c r="I520" t="n">
+        <v>604.52</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="n">
+        <v>519</v>
+      </c>
+      <c r="B521" s="2" t="n">
+        <v>45686</v>
+      </c>
+      <c r="C521" t="n">
+        <v>0.009160360729221185</v>
+      </c>
+      <c r="D521" t="n">
+        <v>0.0136330129726704</v>
+      </c>
+      <c r="E521" t="n">
+        <v>-0.004847849515832268</v>
+      </c>
+      <c r="F521" t="n">
+        <v>-0.01973957897084391</v>
+      </c>
+      <c r="G521" t="n">
+        <v>-0.001399612392022003</v>
+      </c>
+      <c r="H521" t="n">
+        <v>-0.004465339561033602</v>
+      </c>
+      <c r="I521" t="n">
+        <v>601.8099999999999</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="n">
+        <v>520</v>
+      </c>
+      <c r="B522" s="2" t="n">
+        <v>45687</v>
+      </c>
+      <c r="C522" t="n">
+        <v>-0.00152087511781882</v>
+      </c>
+      <c r="D522" t="n">
+        <v>-0.02543769027733501</v>
+      </c>
+      <c r="E522" t="n">
+        <v>-0.006500610052404535</v>
+      </c>
+      <c r="F522" t="n">
+        <v>0.03712443706234334</v>
+      </c>
+      <c r="G522" t="n">
+        <v>0.005586601499866716</v>
+      </c>
+      <c r="H522" t="n">
+        <v>0.008162198247832665</v>
+      </c>
+      <c r="I522" t="n">
+        <v>605.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
